--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NORTH_CAROLINA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NORTH_CAROLINA_2011.xlsx
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C175">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C202">
@@ -6493,7 +6493,7 @@
         <v>233</v>
       </c>
       <c r="D341">
-        <v>0.009092328104269</v>
+        <v>0.009092328104269002</v>
       </c>
     </row>
     <row r="342">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C715">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C810">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C811">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C842">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C843">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="B1220" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1220">
@@ -22812,7 +22812,7 @@
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1248">
@@ -25638,7 +25638,7 @@
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1405">
